--- a/vending_machine_refactor/data/vending_machine.xlsx
+++ b/vending_machine_refactor/data/vending_machine.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="machine_config" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="session_state" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_log" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stock_log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cash_inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="machine_config" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="session_state" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sales_log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cash_log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="stock_log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="audit_log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -502,7 +502,7 @@
         <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
         <v>20</v>
@@ -514,7 +514,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>images/P001.jpg</t>
+          <t>images/water.jpg</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -536,7 +536,7 @@
         <v>500</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>images/P002.jpg</t>
+          <t>images/coffee_cup.jpg</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -570,7 +570,7 @@
         <v>550</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>images/P003.jpg</t>
+          <t>images/ion_drink.jpg</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -604,7 +604,7 @@
         <v>700</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -616,7 +616,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>images/P004.jpg</t>
+          <t>images/letsbe.jpg</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -638,7 +638,7 @@
         <v>750</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>images/P005.jpg</t>
+          <t>images/cider.jpg</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -672,7 +672,7 @@
         <v>800</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
@@ -684,7 +684,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>images/P006.jpg</t>
+          <t>images/special_drink.jpg</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1025,11 +1025,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1086,6 +1086,903 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SALE-20260326000634183762</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:34</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>800</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4700</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SALE-20260326001313243528</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:13</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SALE-20260326001313946131</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SALE-20260326001314443669</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>800</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SALE-20260326001318638466</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>750</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>750</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SALE-20260326001318885059</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>750</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>750</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SALE-20260326001319140452</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>750</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>750</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SALE-20260326001319397739</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>750</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>750</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SALE-20260326001319655454</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>750</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>750</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SALE-20260326001319923309</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>750</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>750</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SALE-20260326001323223620</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>700</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>700</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SALE-20260326001323497705</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>700</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>700</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SALE-20260326001323778754</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>700</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>700</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SALE-20260326001324043692</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>700</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>700</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SALE-20260326001330869076</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>700</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>700</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SALE-20260326001331148574</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>700</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SALE-20260326001339219484</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>750</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>750</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SALE-20260326001339523153</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>750</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>750</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SALE-20260326001339813615</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>800</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>800</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SALE-20260326001340198827</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>700</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>700</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SALE-20260326001340522347</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>700</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>700</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SALE-20260326001340883539</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>이온음료</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>550</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>550</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SALE-20260326001341189490</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:41</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>이온음료</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>550</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>550</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1097,16 +1994,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,6 +2040,1556 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASH-20260326000629749980</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:29</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASH-20260326000630299857</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASH-20260326000630844461</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASH-20260326000631333398</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASH-20260326000631842659</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASH-20260326000632986992</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:32</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>500</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASH-20260326000634183779</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:34</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DISPENSE_CHANGE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>purchase_change:P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CASH-20260326000634183789</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:34</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DISPENSE_CHANGE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>purchase_change:P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CASH-20260326000634183798</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:34</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DISPENSE_CHANGE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>purchase_change:P006</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CASH-20260326001311198731</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CASH-20260326001311432353</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CASH-20260326001311654689</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CASH-20260326001311873728</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CASH-20260326001312079948</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CASH-20260326001314937599</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>500</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CASH-20260326001315832937</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CASH-20260326001316461227</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CASH-20260326001317120219</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CASH-20260326001320279198</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CASH-20260326001320524717</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CASH-20260326001320781573</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CASH-20260326001321014068</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CASH-20260326001324527794</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CASH-20260326001324908252</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CASH-20260326001325169457</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CASH-20260326001325435869</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CASH-20260326001325676502</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CASH-20260326001325954480</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CASH-20260326001326202521</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:26</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CASH-20260326001326478270</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CASH-20260326001326727084</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CASH-20260326001326991982</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CASH-20260326001329275697</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CASH-20260326001329541791</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CASH-20260326001329807605</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:29</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CASH-20260326001330072260</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CASH-20260326001330329761</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CASH-20260326001331781753</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>300</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CASH-20260326001331781772</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>500</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>500</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CASH-20260326001331781783</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CASH-20260326001336709716</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:36</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CASH-20260326001336998066</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:36</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CASH-20260326001337300351</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:37</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CASH-20260326001337559223</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:37</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CASH-20260326001337870748</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:37</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>user_insert</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CASH-20260326001342100341</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:42</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>REFUND</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>200</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>user_refund</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CASH-20260326001439751838</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:39</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CASH-20260326001439751857</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:39</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" t="n">
+        <v>350</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CASH-20260326001439751866</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:39</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COLLECT</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>17</v>
+      </c>
+      <c r="F50" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>admin_collect_keep_min</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CASH-20260326001448003477</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:48</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>REFILL_CASH</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>100</v>
+      </c>
+      <c r="E51" t="n">
+        <v>7</v>
+      </c>
+      <c r="F51" t="n">
+        <v>700</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>admin_refill_to_minimum</t>
         </is>
       </c>
     </row>
@@ -1157,18 +3604,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1215,6 +3662,1195 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STOCK-20260326000634183806</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:06:34</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001313243543</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:13</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001313946145</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001314443683</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001318638480</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001318885073</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001319140474</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001319397755</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001319655474</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001319923324</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001323223636</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001323497721</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001323778776</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001324043710</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001330869091</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001331148594</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001339219515</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001339523175</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001339813630</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:39</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001340198848</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001340522363</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001340883561</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:40</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>이온음료</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001341189505</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:13:41</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>이온음료</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SALE</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001432256541</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:32</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>샘물</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>13</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001433552416</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:33</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>커피</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001434650738</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:34</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>이온음료</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001435377260</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:35</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>고급커피</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>18</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001436138967</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:36</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>탄산음료</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STOCK-20260326001436930132</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:36</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>특화음료</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>REFILL</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>admin_refill_to_max</t>
         </is>
       </c>
     </row>
@@ -1229,15 +4865,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1272,6 +4908,358 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001432256565</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>before=13, added=7, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001433552441</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:33</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>before=10, added=10, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001434650755</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:34</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>before=8, added=12, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001435377285</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:35</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>before=2, added=18, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001436138988</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:36</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>before=2, added=18, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001436930156</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:36</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PRODUCT_REFILL_TO_MAX</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>before=5, added=15, after=20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001439751877</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:39</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CASH_COLLECT</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>keep_minimum=True, total_amount=17400</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001448003506</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:48</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CASH_REFILL_TO_MINIMUM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>minimum cash baseline restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001450368337</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CASH_COLLECT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>keep_minimum=True, total_amount=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001452882362</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:52</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CASH_REFILL_TO_MINIMUM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>minimum cash baseline restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AUDIT-20260326001453881315</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-26 00:14:53</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CASH_COLLECT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>cash_inventory</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>keep_minimum=True, total_amount=0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
